--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_339_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_339_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M3" t="n">
         <v>10</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,7 +1335,7 @@
         <v>20</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>3</v>
@@ -1929,10 +1929,10 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X20" t="n">
         <v>3</v>
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2315,16 +2315,16 @@
         <v>19</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U22" t="n">
         <v>3</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
         <v>6</v>
@@ -2514,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3298,13 +3298,13 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
         <v>4</v>
@@ -3827,16 +3827,16 @@
         <v>136</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U30" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X30" t="n">
         <v>35</v>
@@ -4295,13 +4295,13 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X35" t="n">
         <v>3</v>
@@ -4488,10 +4488,10 @@
         <v>18</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -4690,10 +4690,10 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X37" t="n">
         <v>6</v>
@@ -4886,10 +4886,10 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X38" t="n">
         <v>1</v>
@@ -5079,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -5468,16 +5468,16 @@
         <v>14</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X41" t="n">
         <v>5</v>
@@ -5664,7 +5664,7 @@
         <v>19</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -5866,10 +5866,10 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X43" t="n">
         <v>1</v>
@@ -6196,16 +6196,16 @@
         <v>122</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X45" t="n">
         <v>31</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_339_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_339_EL.xlsx
@@ -674,10 +674,10 @@
         <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="O2" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="P2" t="n">
         <v>4</v>
@@ -695,17 +695,17 @@
         <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V2" t="n">
         <v>9</v>
       </c>
       <c r="W2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>87.50</t>
+          <t>80.77</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="O3" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P3" t="n">
         <v>8</v>
@@ -851,20 +851,20 @@
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>70.83</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>43.48</t>
+          <t>38.10</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1739,10 +1739,10 @@
         <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -1935,10 +1935,10 @@
         <v>2</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -2131,10 +2131,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -2327,14 +2327,14 @@
         <v>1</v>
       </c>
       <c r="X22" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y22" t="n">
         <v>6</v>
       </c>
-      <c r="Y22" t="n">
-        <v>8</v>
-      </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -2363,22 +2363,22 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AJ22" t="n">
         <v>2</v>
       </c>
       <c r="AK22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -2523,14 +2523,14 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y23" t="n">
         <v>5</v>
       </c>
-      <c r="Y23" t="n">
-        <v>6</v>
-      </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -2719,14 +2719,14 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -2915,14 +2915,14 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3343,7 +3343,7 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
@@ -3354,11 +3354,11 @@
         <v>1</v>
       </c>
       <c r="AK27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -3839,14 +3839,14 @@
         <v>5</v>
       </c>
       <c r="X30" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="Y30" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3875,22 +3875,22 @@
         <v>4</v>
       </c>
       <c r="AH30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
         <v>9</v>
       </c>
       <c r="AK30" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4304,10 +4304,10 @@
         <v>3</v>
       </c>
       <c r="X35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -4337,25 +4337,25 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ35" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK35" t="n">
         <v>5</v>
       </c>
-      <c r="AK35" t="n">
-        <v>6</v>
-      </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -4500,14 +4500,14 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -4696,10 +4696,10 @@
         <v>2</v>
       </c>
       <c r="X37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -5284,14 +5284,14 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5480,14 +5480,14 @@
         <v>2</v>
       </c>
       <c r="X41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5676,14 +5676,14 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y42" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA42" t="n">
@@ -5709,25 +5709,25 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
@@ -6208,14 +6208,14 @@
         <v>10</v>
       </c>
       <c r="X45" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="Y45" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="AA45" t="n">
@@ -6241,25 +6241,25 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH45" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AK45" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
